--- a/output_boron/boron_Intermediate_badger_2013.xlsx
+++ b/output_boron/boron_Intermediate_badger_2013.xlsx
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">10.1002/palo.20015</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/boron_isotopes_badger_2013.xlsx</t>
+    <t xml:space="preserve">boron_isotopes_badger_2013_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1399,7 +1399,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1459,12 +1459,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1578,7 +1572,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1660,7 +1654,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2267,7 +2260,7 @@
       <c r="B5" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" t="s">
         <v>242</v>
       </c>
       <c r="D5" t="s">
@@ -2344,7 +2337,7 @@
       <c r="B6" t="s">
         <v>241</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" t="s">
         <v>242</v>
       </c>
       <c r="D6" t="s">
@@ -2421,7 +2414,7 @@
       <c r="B7" t="s">
         <v>241</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" t="s">
         <v>242</v>
       </c>
       <c r="D7" t="s">
@@ -2498,7 +2491,7 @@
       <c r="B8" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" t="s">
         <v>242</v>
       </c>
       <c r="D8" t="s">
@@ -2575,7 +2568,7 @@
       <c r="B9" t="s">
         <v>241</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" t="s">
         <v>242</v>
       </c>
       <c r="D9" t="s">
@@ -2652,7 +2645,7 @@
       <c r="B10" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" t="s">
         <v>242</v>
       </c>
       <c r="D10" t="s">
@@ -3021,14 +3014,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
